--- a/results/Int Task Remove ACC -0.4/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_9_permute.xlsx
@@ -440,347 +440,347 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6269528313992924</v>
+        <v>0.6323003171460522</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6305880951071514</v>
+        <v>0.6360620726319456</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6294185044638765</v>
+        <v>0.6307989147372087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6312783002438175</v>
+        <v>0.6377321307448349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6295844103466608</v>
+        <v>0.6381271883994207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6269317494362867</v>
+        <v>0.6381271883994207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6334488258263213</v>
+        <v>0.6342600230984986</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6320922473372564</v>
+        <v>0.6303534436928266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6310885625767659</v>
+        <v>0.6344653430860328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6365808722433042</v>
+        <v>0.638827476214046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.636246310656474</v>
+        <v>0.6437744046636968</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6356193514088251</v>
+        <v>0.6437744046636968</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6393783570734569</v>
+        <v>0.6263542869713469</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6368494381198555</v>
+        <v>0.6306825056371336</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6360144090634109</v>
+        <v>0.6352765403582101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.635116134117949</v>
+        <v>0.6430237034592752</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.635116134117949</v>
+        <v>0.6416643751489486</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6351793800069663</v>
+        <v>0.6393325267190966</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6340941172157144</v>
+        <v>0.6331527617371537</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6281013400795614</v>
+        <v>0.6808878256246678</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6295422464206493</v>
+        <v>0.6780243450842363</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6192661643659829</v>
+        <v>0.6756906634402098</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6069515481493704</v>
+        <v>0.674081101395076</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.612970906891052</v>
+        <v>0.674081101395076</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.619092925626501</v>
+        <v>0.6821894076885002</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.619092925626501</v>
+        <v>0.6755064254156813</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6289372857430934</v>
+        <v>0.6793919228583476</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6340767016810573</v>
+        <v>0.6782984106033108</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6254440961337513</v>
+        <v>0.6901290582778786</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6016205613301802</v>
+        <v>0.6767814258739848</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6087041009001082</v>
+        <v>0.6767814258739848</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.488889805495976</v>
+        <v>0.6729325927148069</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5034491924691562</v>
+        <v>0.6694394031054649</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5072091147408753</v>
+        <v>0.6635887000678289</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5174851967955416</v>
+        <v>0.6643476507360355</v>
       </c>
     </row>
     <row r="37">
@@ -790,57 +790,57 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5170479752149444</v>
+        <v>0.660380575262608</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5162129461584997</v>
+        <v>0.6778226915250509</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5146455480393775</v>
+        <v>0.6736869603475775</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4734055619718052</v>
+        <v>0.6289262864580469</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4874571486186731</v>
+        <v>0.6411886560706888</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4729215934297604</v>
+        <v>0.5950283231589947</v>
       </c>
     </row>
     <row r="43">
@@ -850,477 +850,477 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4829868558543695</v>
+        <v>0.6126088470916058</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4926753927661369</v>
+        <v>0.609379640323379</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4759821444939413</v>
+        <v>0.6075565088269264</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.479367174466993</v>
+        <v>0.6382637628554144</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.468586041907276</v>
+        <v>0.6271150708537279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4642367412784836</v>
+        <v>0.6171744669929788</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4648242864213826</v>
+        <v>0.6501109094575519</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4541082329648573</v>
+        <v>0.6508643604832353</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.454400630625676</v>
+        <v>0.6487992447157601</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4576775009624374</v>
+        <v>0.6499266714330235</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4468166235861336</v>
+        <v>0.6149425287356322</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4456048690168473</v>
+        <v>0.6140864177161818</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4525325853819502</v>
+        <v>0.6127875854736109</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4531806265926048</v>
+        <v>0.588168435718345</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4395589286696365</v>
+        <v>0.5885451612311866</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4436607453848833</v>
+        <v>0.5684210526315789</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4420328511980054</v>
+        <v>0.5525793323433977</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4737859539129957</v>
+        <v>0.5518918770279931</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4752057782910777</v>
+        <v>0.5509725201195256</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4741415974628316</v>
+        <v>0.5235082219655722</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4348659003831418</v>
+        <v>0.5132853031219637</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4348659003831418</v>
+        <v>0.5156217345872518</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4474609983684393</v>
+        <v>0.5189591009917689</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.434168362389778</v>
+        <v>0.4871106711397092</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4952024785055638</v>
+        <v>0.5096042090597445</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.494219875708079</v>
+        <v>0.5096042090597445</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4999835010724303</v>
+        <v>0.5486727529377258</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4976360703220958</v>
+        <v>0.5535481860345745</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4984500174155346</v>
+        <v>0.5604859850776367</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4984500174155346</v>
+        <v>0.5206291591046582</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4957762745421548</v>
+        <v>0.5032667876588022</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4930814497057691</v>
+        <v>0.4985994243707492</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4928678802544501</v>
+        <v>0.4879319510898458</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4837375570587912</v>
+        <v>0.4989697336339805</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4679370840895342</v>
+        <v>0.5100625126033475</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.459633540486535</v>
+        <v>0.5100625126033475</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4638545161231187</v>
+        <v>0.5100625126033475</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4608984582668793</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4818163486040074</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4858915837137253</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.474846468312893</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5000641624961044</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.487594639681754</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4877422134227942</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4980705420814314</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5024271755669215</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5024271755669215</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5020614493391262</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
